--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_234_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_234_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6254</v>
+        <v>2.5481</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1877</v>
+        <v>0.48</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4377</v>
+        <v>2.068</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4605</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9984</v>
+        <v>0.921</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0657</v>
+        <v>0.358</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9326</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3016</v>
+        <v>1.3756</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2368</v>
+        <v>1.0756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0648</v>
+        <v>0.3</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2197</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1024</v>
+        <v>-0.0283</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2592</v>
+        <v>-0.4204</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1568</v>
+        <v>0.3921</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2508</v>
+        <v>1.2918</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1492</v>
+        <v>-0.0746</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.3664</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7634</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1687</v>
+        <v>-0.094</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0953</v>
+        <v>0.0617</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2491</v>
+        <v>-0.3473</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1712</v>
+        <v>-1.1535</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.922</v>
+        <v>0.8062</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.904</v>
+        <v>-2.2084</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9328</v>
+        <v>1.0273</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8369</v>
+        <v>-3.2357</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9507</v>
+        <v>-0.2894</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.1028</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1104</v>
+        <v>-1.3922</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8547</v>
+        <v>-1.919</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0926</v>
+        <v>-0.0755</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9473</v>
+        <v>-1.8435</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3851</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6122</v>
+        <v>0.0121</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2271</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4817</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8676</v>
+        <v>2.6149</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3494</v>
+        <v>-3.3029</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3963</v>
+        <v>2.0755</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3336</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3279</v>
+        <v>2.409</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4364</v>
+        <v>2.7405</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2892</v>
+        <v>0.0672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>2.6733</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8327</v>
+        <v>-0.6651</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3577</v>
+        <v>-0.4008</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4751</v>
+        <v>-0.2643</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.827</v>
+        <v>-0.0108</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4312</v>
+        <v>-0.1256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3958</v>
+        <v>0.1149</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1444</v>
+        <v>-3.2166</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1444</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2215</v>
+        <v>-0.8953</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1285</v>
+        <v>-1.9278</v>
       </c>
       <c r="F7" t="n">
-        <v>0.907</v>
+        <v>1.0325</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2084</v>
+        <v>-0.7624</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0273</v>
+        <v>-2.6495</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2357</v>
+        <v>1.8871</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2894</v>
+        <v>0.5458</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1028</v>
+        <v>-2.2379</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3922</v>
+        <v>2.7837</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.919</v>
+        <v>-1.3082</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0755</v>
+        <v>-0.4116</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8435</v>
+        <v>-0.8966</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2245</v>
+        <v>0.3284</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.963</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7385</v>
+        <v>0.3949</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2836</v>
+        <v>0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2681</v>
+        <v>-1.3171</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0684</v>
+        <v>0.9987</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3365</v>
+        <v>-2.3158</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0755</v>
+        <v>-0.3963</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3336</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.409</v>
+        <v>-0.3279</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7405</v>
+        <v>0.4364</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0672</v>
+        <v>0.2892</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6733</v>
+        <v>0.1472</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6651</v>
+        <v>-0.8327</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4008</v>
+        <v>-0.3577</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2643</v>
+        <v>-0.4751</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5909</v>
+        <v>0.9917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.5623</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0813</v>
+        <v>0.4294</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.2166</v>
+        <v>-2.1444</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2166</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7614</v>
+        <v>-1.536</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5922</v>
+        <v>-0.2442</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8309</v>
+        <v>-1.2917</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7624</v>
+        <v>-0.904</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6495</v>
+        <v>0.9328</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8871</v>
+        <v>-1.8369</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5458</v>
+        <v>0.9507</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2379</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7837</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3082</v>
+        <v>-1.8547</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4116</v>
+        <v>0.0926</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>-1.9473</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.4793</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5377</v>
+        <v>-0.4</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>0.1968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1933</v>
+        <v>-0.5968</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1575</v>
+        <v>-1.8806</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3447</v>
+        <v>-0.0341</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8129</v>
+        <v>-1.8465</v>
       </c>
       <c r="G10" t="n">
         <v>-1.813</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4141</v>
+        <v>-1.1371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6642</v>
+        <v>-0.3536</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7499</v>
+        <v>-0.7835</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4061</v>
+        <v>-3.6923</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5975</v>
+        <v>-0.2869</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8086</v>
+        <v>-3.4054</v>
       </c>
       <c r="G11" t="n">
         <v>0.0148</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4725</v>
+        <v>-0.7587</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0114</v>
+        <v>0.2992</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4611</v>
+        <v>-1.0578</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3247</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0807</v>
+        <v>-5.6596</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1558</v>
+        <v>-4.802</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.8577</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3475</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8776</v>
+        <v>-1.4565</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8804</v>
+        <v>-0.5265</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9972</v>
+        <v>-0.93</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3557</v>
+        <v>-9.7585</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7275</v>
+        <v>-7.063</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6282</v>
+        <v>-2.6954</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0661</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8257</v>
+        <v>-1.2285</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1123</v>
+        <v>-0.4479</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7134</v>
+        <v>-0.7806</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.3058</v>
+        <v>-20.5592</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.1637</v>
+        <v>-10.4169</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.1421</v>
+        <v>-10.1423</v>
       </c>
       <c r="G14" t="n">
         <v>-14.851</v>
@@ -1537,7 +1537,7 @@
         <v>-14.7548</v>
       </c>
       <c r="P14" t="n">
-        <v>2.319600000000002</v>
+        <v>2.3196</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2367</v>
@@ -1546,10 +1546,10 @@
         <v>18.5565</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.9083</v>
+        <v>-2.1614</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3532</v>
+        <v>-0.6062000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>-1.5551</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.435600000000001</v>
+        <v>7.5252</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7742</v>
+        <v>5.2297</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6614</v>
+        <v>2.2955</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2239</v>
+        <v>5.3085</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2769</v>
+        <v>5.4188</v>
       </c>
       <c r="I15" t="n">
-        <v>0.947</v>
+        <v>-0.1103</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5275</v>
+        <v>5.4585</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5768</v>
+        <v>4.7726</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9507</v>
+        <v>0.6859</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3036</v>
+        <v>-0.1499</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.6462</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0037</v>
+        <v>-0.7961</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2839</v>
+        <v>1.0543</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4065</v>
+        <v>0.0907</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1226</v>
+        <v>0.9636</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
         <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3939</v>
+        <v>7.3734</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6399</v>
+        <v>5.0049</v>
       </c>
       <c r="F16" t="n">
-        <v>2.754</v>
+        <v>2.3685</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3085</v>
+        <v>3.2239</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4188</v>
+        <v>2.2769</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1103</v>
+        <v>0.947</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4585</v>
+        <v>3.5275</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7726</v>
+        <v>1.5768</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6859</v>
+        <v>1.9507</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1499</v>
+        <v>-0.3036</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6462</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7961</v>
+        <v>-1.0037</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.923</v>
+        <v>1.2217</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4991</v>
+        <v>0.6372</v>
       </c>
       <c r="U16" t="n">
-        <v>1.422</v>
+        <v>0.5845</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6574</v>
+        <v>4.2414</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2947</v>
+        <v>4.587</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6373</v>
+        <v>-0.3456</v>
       </c>
       <c r="G17" t="n">
         <v>2.0673</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7345</v>
+        <v>0.3185</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1404</v>
+        <v>0.4327</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4059</v>
+        <v>-0.1142</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2953</v>
+        <v>3.2235</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0742</v>
+        <v>0.3172</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2211</v>
+        <v>2.9063</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5917</v>
+        <v>4.9711</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5511</v>
+        <v>1.15</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0406</v>
+        <v>3.8211</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3878</v>
+        <v>3.7451</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1814</v>
+        <v>0.1785</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5692</v>
+        <v>3.5666</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2039</v>
+        <v>1.226</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.9715</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>0.2545</v>
       </c>
       <c r="P18" t="n">
         <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-3.7112</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3532</v>
+        <v>0.9482</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5149</v>
+        <v>0.2833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1617</v>
+        <v>0.6649</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0332</v>
+        <v>2.5147</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3905</v>
+        <v>0.428</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4237</v>
+        <v>2.0867</v>
       </c>
       <c r="G19" t="n">
-        <v>4.9711</v>
+        <v>1.5917</v>
       </c>
       <c r="H19" t="n">
-        <v>1.15</v>
+        <v>0.5511</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8211</v>
+        <v>1.0406</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7451</v>
+        <v>1.3878</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1785</v>
+        <v>-0.1814</v>
       </c>
       <c r="L19" t="n">
-        <v>3.5666</v>
+        <v>1.5692</v>
       </c>
       <c r="M19" t="n">
-        <v>1.226</v>
+        <v>0.2039</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9715</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2545</v>
+        <v>-0.5286</v>
       </c>
       <c r="P19" t="n">
         <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.7112</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.242</v>
+        <v>-0.1338</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4244</v>
+        <v>-0.161</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1823</v>
+        <v>0.0272</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3069</v>
+        <v>1.6265</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1011</v>
+        <v>1.219</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2058</v>
+        <v>0.4075</v>
       </c>
       <c r="G20" t="n">
         <v>2.5642</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0975</v>
+        <v>0.2221</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0228</v>
+        <v>0.1788</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4311</v>
+        <v>0.7814</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8072</v>
+        <v>-1.3354</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3761</v>
+        <v>2.1168</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6614</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5403</v>
+        <v>0.6721</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6563</v>
+        <v>-0.1845</v>
       </c>
       <c r="U21" t="n">
-        <v>0.116</v>
+        <v>0.8566</v>
       </c>
       <c r="V21" t="n">
         <v>1.4665</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2535</v>
+        <v>-0.6923</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5493</v>
+        <v>-0.3134</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7042</v>
+        <v>-0.3789</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6257</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8984</v>
+        <v>-0.3372</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3835</v>
+        <v>-0.0582</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4254</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3593</v>
+        <v>-0.7776</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6713</v>
+        <v>-3.498</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6879999999999999</v>
+        <v>2.7203</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9156</v>
+        <v>-1.6729</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2436</v>
+        <v>-0.2207</v>
       </c>
       <c r="I23" t="n">
-        <v>0.328</v>
+        <v>-1.4522</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8398</v>
+        <v>-1.1905</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5391</v>
+        <v>-0.5847</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6993</v>
+        <v>-0.6058</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0759</v>
+        <v>-0.4824</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7045</v>
+        <v>0.364</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3713</v>
+        <v>-0.8464</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>1.198</v>
+        <v>0.8953</v>
       </c>
       <c r="T23" t="n">
-        <v>1.274</v>
+        <v>0.244</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.076</v>
+        <v>0.6513</v>
       </c>
       <c r="V23" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7726</v>
+        <v>-2.1513</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3236</v>
+        <v>-1.497</v>
       </c>
       <c r="F24" t="n">
-        <v>2.551</v>
+        <v>-0.6543</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6729</v>
+        <v>-1.9156</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2207</v>
+        <v>-2.2436</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4522</v>
+        <v>0.328</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1905</v>
+        <v>-0.8398</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5847</v>
+        <v>-1.5391</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6058</v>
+        <v>0.6993</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4824</v>
+        <v>-1.0759</v>
       </c>
       <c r="N24" t="n">
-        <v>0.364</v>
+        <v>-0.7045</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8464</v>
+        <v>-0.3713</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0997</v>
+        <v>0.4059</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5816</v>
+        <v>0.4483</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4819</v>
+        <v>-0.0424</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.3058</v>
+        <v>23.6649</v>
       </c>
       <c r="E25" t="n">
-        <v>10.1422</v>
+        <v>10.142</v>
       </c>
       <c r="F25" t="n">
-        <v>11.1636</v>
+        <v>13.5228</v>
       </c>
       <c r="G25" t="n">
         <v>14.8511</v>
       </c>
       <c r="H25" t="n">
-        <v>6.452399999999999</v>
+        <v>6.4524</v>
       </c>
       <c r="I25" t="n">
         <v>8.3986</v>
@@ -2392,7 +2392,7 @@
         <v>3.855599999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.3561</v>
+        <v>-6.356100000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-2.3196</v>
@@ -2404,13 +2404,13 @@
         <v>16.2367</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9083</v>
+        <v>5.2671</v>
       </c>
       <c r="T25" t="n">
         <v>1.555</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3531</v>
+        <v>3.7121</v>
       </c>
       <c r="V25" t="n">
         <v>5.866</v>
